--- a/tests/e2e/Intent_Test_Matrix.xlsx
+++ b/tests/e2e/Intent_Test_Matrix.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Saves name, asks for company</t>
+          <t>Saves name, asks for email</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Uses generic name, moves to company step</t>
+          <t>Uses generic name, asks for email</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Extracts 'Darshit', asks for company</t>
+          <t>Extracts 'Darshit', asks for email</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Company step - normal</t>
+          <t>Industry step - normal</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Saves company, completes onboarding</t>
+          <t>Saves industry, completes onboarding</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Company step - skip</t>
+          <t>Industry step - skip</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Uses name as company, completes onboarding</t>
+          <t>Uses name as industry, completes onboarding</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Extracts name, asks for company</t>
+          <t>Extracts name, asks for email</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Returns SUM for Jan-Mar 2026 (correct quarter)</t>
+          <t>Returns SUM for the correct calendar quarter, relative to when the test runs</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
